--- a/docentes/Hernández Cides Ricardo - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Cides Ricardo - Estadisticos 20232.xlsx
@@ -559,16 +559,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H2">
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -582,16 +585,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H3">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -647,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>97.62</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -673,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>97.62</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Cides Ricardo - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Cides Ricardo - Estadisticos 20232.xlsx
@@ -653,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>95.23999999999999</v>
+        <v>97.62</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -679,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>95.23999999999999</v>
+        <v>97.62</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
